--- a/Handbook v2.xlsx
+++ b/Handbook v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\young\Dropbox\Michael\Work-Uni-Coding\Youngs Farm Analysis\FOG\Work\R&amp;D\Carla - NRM\NRM App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82D4DEE-D1DD-447D-ACDB-4A155882AD34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242C0731-B24A-4D34-BE19-DA387820C671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{E8213FCE-A24F-4DC8-8C58-DD7521FC127C}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8213FCE-A24F-4DC8-8C58-DD7521FC127C}"/>
   </bookViews>
   <sheets>
     <sheet name="Guide" sheetId="2" r:id="rId1"/>
@@ -1440,10 +1440,10 @@
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.000%"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.000%"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="\$#,##0.00"/>
   </numFmts>
   <fonts count="40">
     <font>
@@ -2246,7 +2246,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -2329,7 +2329,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="11" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="3" fillId="12" borderId="0" xfId="11" applyNumberFormat="1" applyFill="1"/>
@@ -2457,7 +2457,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="7" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="12" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="12" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="7" applyBorder="1" applyAlignment="1">
@@ -2507,9 +2507,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="20" xfId="15" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="10" fillId="3" borderId="23" xfId="6" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="10" fillId="3" borderId="24" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="24" xfId="6" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="10" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="10" borderId="0" xfId="12" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="3" fillId="10" borderId="0" xfId="12" applyNumberFormat="1"/>
@@ -2524,16 +2524,16 @@
     <xf numFmtId="0" fontId="35" fillId="20" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="19" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="19" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="20" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="19" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="19" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="19" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="19" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="19" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2551,10 +2551,10 @@
     <xf numFmtId="1" fontId="10" fillId="3" borderId="3" xfId="6" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="3" borderId="3" xfId="6" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="3" xfId="6" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="3" xfId="6" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="3" xfId="6" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="10" fillId="3" borderId="3" xfId="6" applyNumberFormat="1" applyAlignment="1">
@@ -2578,10 +2578,10 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2596,10 +2596,10 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2610,7 +2610,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="31" fillId="16" borderId="8" xfId="16" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="10" fillId="3" borderId="3" xfId="6" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="3" xfId="6" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="23" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2620,13 +2620,13 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="6" applyBorder="1"/>
     <xf numFmtId="6" fontId="10" fillId="3" borderId="23" xfId="6" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="24" xfId="6" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="38" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="3" borderId="3" xfId="6" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="3" xfId="6" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="6" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="10" fillId="3" borderId="3" xfId="6" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2662,6 +2662,7 @@
     <xf numFmtId="0" fontId="39" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="17">
     <cellStyle name="20% - Accent6" xfId="10" builtinId="50"/>
@@ -2788,7 +2789,7 @@
                   <c:v>169</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>116.34926603661927</c:v>
+                  <c:v>-116.34926603661927</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2</c:v>
@@ -13350,7 +13351,7 @@
       <c r="E259" s="7"/>
       <c r="G259" s="49">
         <f ca="1">SUM(G265:G274)</f>
-        <v>3546.0703719601315</v>
+        <v>3313.3718398868932</v>
       </c>
       <c r="H259" s="13" t="s">
         <v>118</v>
@@ -13459,7 +13460,7 @@
       <c r="F266" s="22"/>
       <c r="G266" s="49">
         <f ca="1">Database!E7</f>
-        <v>116.34926603661927</v>
+        <v>-116.34926603661927</v>
       </c>
       <c r="H266" s="22" t="s">
         <v>19</v>
@@ -13629,7 +13630,7 @@
       <c r="E275" s="7"/>
       <c r="G275" s="49">
         <f ca="1">SUM(G265:G274)</f>
-        <v>3546.0703719601315</v>
+        <v>3313.3718398868932</v>
       </c>
       <c r="H275" s="13" t="s">
         <v>118</v>
@@ -18806,12 +18807,12 @@
         <v>1</v>
       </c>
       <c r="C7" s="125">
-        <f ca="1">Calculations!B19</f>
-        <v>116.34926603661927</v>
-      </c>
-      <c r="E7" s="46">
-        <f t="shared" ca="1" si="0"/>
-        <v>116.34926603661927</v>
+        <f ca="1">-Calculations!B19</f>
+        <v>-116.34926603661927</v>
+      </c>
+      <c r="E7" s="182">
+        <f ca="1">C7</f>
+        <v>-116.34926603661927</v>
       </c>
     </row>
     <row r="8" spans="1:9">
